--- a/stories/arbres/ATOM-FAM.VER.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Daphné est dans la cuisine. Elle veut verser l'eau. Le verre bascule. L'eau va sur la table. Daphné sent son ventre serré. Elle va vers maman. Elle raconte. Elle dit : l'eau est sur la table. Maman écoute. Maman dit : merci d'avoir raconté. Papa arrive. Daphné raconte aussi à papa. Papa tend une éponge. Ils essuient ensemble. Plus tard, Daphné froisse un dessin de papa. Elle sent encore son ventre. Elle va vers papa et maman. Elle raconte. Papa dit : merci. On dit à papa ou maman ce qui s'est passé. Raconter aide. Daphné est entourée.</t>
+          <t>Daphné est dans la cuisine. Elle veut verser l'eau. Le verre bascule. L'eau va sur la table. Daphné sent son ventre serré. Elle va vers maman. Elle raconte. L'eau est sur la table. Maman écoute. Merci d'avoir raconté. Papa arrive. Daphné raconte aussi à papa. Papa tend une éponge. Ils essuient ensemble. Plus tard, Daphné froisse un dessin de papa. Elle sent encore son ventre. Elle va vers papa et maman. Elle raconte. Merci. On dit à papa ou maman ce qui s'est passé. Raconter aide. Daphné est entourée.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné est dans la cuisine. Elle veut verser l'eau. Le verre bascule. L'eau va sur la table. Daphné sent son ventre serré. Elle va vers maman. Elle raconte.
+narrateur|L'eau est sur la table. Maman écoute.
+maman|Merci d'avoir raconté. Papa arrive.
+narrateur|Daphné raconte aussi à papa. Papa tend une éponge. Ils essuient ensemble. Plus tard, Daphné froisse un dessin de papa. Elle sent encore son ventre. Elle va vers papa et maman. Elle raconte.
+papa|Merci. On dit à papa ou maman ce qui s'est passé. Raconter aide.
+narrateur|Daphné est entourée.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|L'eau est sur la table. Que fait Daphné ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné a raconté. Papa et maman ont écouté. Raconter aide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Daphné pose l'éponge. Maman lui verse un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Daphné est entourée.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|L'eau est sur la table. Que fait Daphné ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Daphné a raconté. Papa et maman ont écouté. Raconter aide.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Daphné pose l'éponge. Maman lui verse un verre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Daphné raconte à papa et maman</t>
+          <t>Sarah raconte l'eau et le dessin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La buée dessine un nuage. Sarah raconte l'eau sur la table, puis le dessin froissé. Papa et maman écoutent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Daphné est dans la cuisine. Elle veut verser l'eau. Le verre bascule. L'eau va sur la table. Daphné sent son ventre serré. Elle va vers maman. Elle raconte. L'eau est sur la table. Maman écoute. Merci d'avoir raconté. Papa arrive. Daphné raconte aussi à papa. Papa tend une éponge. Ils essuient ensemble. Plus tard, Daphné froisse un dessin de papa. Elle sent encore son ventre. Elle va vers papa et maman. Elle raconte. Merci. On dit à papa ou maman ce qui s'est passé. Raconter aide. Daphné est entourée.</t>
+          <t>La buée fait un nuage sur la vitre. Une goutte glisse tout doux. Elle laisse un trait brillant. La maison sent la soupe chaude. Une cuillère en bois repose dans la casserole. Le bois est un peu tiède. Dehors, un oiseau se tait. Le village est calme, derrière la vitre. Papa pose un dessin au salon. Le papier fait un petit bruit. Maman reste près de la casserole. Sarah, tu entends la soupe ? Oui, maman. Ça chuchote. Elle est presque prête. Ça sent bon, ici. En ce moment, Sarah veut verser de l'eau. Le pichet est lourd et froid. Le verre est petit et clair. Sarah tient le pichet des deux mains. Le verre bascule. L'eau va sur la table. Ça fait une petite mare. La mare brille. Une goutte tombe aussi par terre. Sarah sent son ventre serré. Elle va vers maman. Maman, l'eau est sur la table. Merci d'avoir raconté. On essuie ensemble. Maman tend une éponge jaune. L'éponge est molle. Sarah appuie tout doux. La table redevient sèche. J'arrive. Papa entre dans la cuisine. Papa, j'ai raconté. L'eau était sur la table. Merci, Sarah. On dit à papa ou maman ce qui s'est passé. Tu as dit juste ce qu'il fallait. Plus tard, le dessin de papa attend au salon. Le papier est fin et crème. Un crayon bleu repose à côté. Sarah veut le regarder de près. Le dessin se froisse un peu. Sarah sent encore son ventre. Elle va vers papa et maman. Le dessin s'est froissé. C'est moi. Merci de raconter. On le lisse ensemble. Papa lisse le papier avec la paume. Maman pose une main sur l'épaule de Sarah. Raconter aide. On dit à papa ou maman. Sarah souffle. Le ventre se desserre. La buée a presque disparu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Daphné est dans la cuisine. Elle veut verser l'eau. Le verre bascule. L'eau va sur la table. Daphné sent son ventre serré. Elle va vers maman. Elle raconte.
-narrateur|L'eau est sur la table. Maman écoute.
-maman|Merci d'avoir raconté. Papa arrive.
-narrateur|Daphné raconte aussi à papa. Papa tend une éponge. Ils essuient ensemble. Plus tard, Daphné froisse un dessin de papa. Elle sent encore son ventre. Elle va vers papa et maman. Elle raconte.
-papa|Merci. On dit à papa ou maman ce qui s'est passé. Raconter aide.
-narrateur|Daphné est entourée.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La buée fait un nuage sur la vitre.
+narrateur|Une goutte glisse tout doux.
+narrateur|Elle laisse un trait brillant.
+narrateur|La maison sent la soupe chaude.
+narrateur|Une cuillère en bois repose dans la casserole.
+narrateur|Le bois est un peu tiède.
+narrateur|Dehors, un oiseau se tait.
+narrateur|Le village est calme, derrière la vitre.
+narrateur|Papa pose un dessin au salon.
+narrateur|Le papier fait un petit bruit.
+narrateur|Maman reste près de la casserole.
+maman|Sarah, tu entends la soupe ?
+enfant-f|Oui, maman.
+enfant-f|Ça chuchote.
+maman|Elle est presque prête.
+papa|Ça sent bon, ici.
+narrateur|En ce moment, Sarah veut verser de l'eau.
+narrateur|Le pichet est lourd et froid.
+narrateur|Le verre est petit et clair.
+narrateur|Sarah tient le pichet des deux mains.
+narrateur|Le verre bascule.
+narrateur|L'eau va sur la table.
+narrateur|Ça fait une petite mare.
+narrateur|La mare brille.
+narrateur|Une goutte tombe aussi par terre.
+narrateur|Sarah sent son ventre serré.
+narrateur|Elle va vers maman.
+enfant-f|Maman, l'eau est sur la table.
+maman|Merci d'avoir raconté.
+maman|On essuie ensemble.
+narrateur|Maman tend une éponge jaune.
+narrateur|L'éponge est molle.
+narrateur|Sarah appuie tout doux.
+narrateur|La table redevient sèche.
+papa|J'arrive.
+narrateur|Papa entre dans la cuisine.
+enfant-f|Papa, j'ai raconté.
+enfant-f|L'eau était sur la table.
+papa|Merci, Sarah.
+papa|On dit à papa ou maman ce qui s'est passé.
+maman|Tu as dit juste ce qu'il fallait.
+narrateur|Plus tard, le dessin de papa attend au salon.
+narrateur|Le papier est fin et crème.
+narrateur|Un crayon bleu repose à côté.
+narrateur|Sarah veut le regarder de près.
+narrateur|Le dessin se froisse un peu.
+narrateur|Sarah sent encore son ventre.
+narrateur|Elle va vers papa et maman.
+enfant-f|Le dessin s'est froissé.
+enfant-f|C'est moi.
+papa|Merci de raconter.
+maman|On le lisse ensemble.
+narrateur|Papa lisse le papier avec la paume.
+narrateur|Maman pose une main sur l'épaule de Sarah.
+papa|Raconter aide.
+maman|On dit à papa ou maman.
+narrateur|Sarah souffle.
+narrateur|Le ventre se desserre.
+narrateur|La buée a presque disparu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>L'eau est sur la table. Que fait Daphné ?</t>
+          <t>L'eau est sur la table. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|L'eau est sur la table. Que fait Daphné ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|L'eau est sur la table.
+narrateur|Que fait Sarah ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Daphné a raconté. Papa et maman ont écouté. Raconter aide.</t>
+          <t>Sarah a raconté. Papa a écouté. Maman a écouté. Tu as dit ce qui s'est passé ? Oui, maman. Bravo, Sarah. Tu as fait du bon travail. L'éponge repose près de l'évier. Elle est encore un peu humide. Le dessin est lisse, sur la table. On raconte à papa ou maman. Sarah pose sa main sur le papier. Le papier est doux. Le crayon est à sa place ? Oui, papa. Le crayon bleu ne roule plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,10 +1737,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Daphné a raconté. Papa et maman ont écouté. Raconter aide.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a raconté.
+narrateur|Papa a écouté.
+narrateur|Maman a écouté.
+maman|Tu as dit ce qui s'est passé ?
+enfant-f|Oui, maman.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'éponge repose près de l'évier.
+narrateur|Elle est encore un peu humide.
+narrateur|Le dessin est lisse, sur la table.
+maman|On raconte à papa ou maman.
+narrateur|Sarah pose sa main sur le papier.
+narrateur|Le papier est doux.
+papa|Le crayon est à sa place ?
+enfant-f|Oui, papa.
+narrateur|Le crayon bleu ne roule plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Daphné pose l'éponge. Maman lui verse un verre.</t>
+          <t>Sarah pose l'éponge. Je te verse un verre ? Oui, maman. Maman verse tout doux. Le verre reste droit. Tu as fini d'essuyer ? Oui, papa. Bravo. La soupe chuchote encore. La buée fait un petit nuage. On goûte dans un moment. Ça sent bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,10 +1915,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Daphné pose l'éponge. Maman lui verse un verre.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah pose l'éponge.
+maman|Je te verse un verre ?
+enfant-f|Oui, maman.
+narrateur|Maman verse tout doux.
+narrateur|Le verre reste droit.
+papa|Tu as fini d'essuyer ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|La soupe chuchote encore.
+narrateur|La buée fait un petit nuage.
+maman|On goûte dans un moment.
+enfant-f|Ça sent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah tient son verre des deux mains. La soupe sent bon. Merci d'avoir raconté. On dit à papa ou maman. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,10 +2093,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah tient son verre des deux mains.
+narrateur|La soupe sent bon.
+maman|Merci d'avoir raconté.
+papa|On dit à papa ou maman.
+enfant-f|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-07.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Daphné est dans la cuisine. Elle veut verser l'eau. Le verre bascule. L'eau va sur la table. Daphné sent son ventre serré. Elle va vers maman. Elle raconte. Elle dit : l'eau est sur la table. Maman écoute. Maman dit : merci d'avoir raconté. Papa arrive. Daphné raconte aussi à papa. Papa tend une éponge. Ils essuient ensemble. Plus tard, Daphné froisse un dessin de papa. Elle sent encore son ventre. Elle va vers papa et maman. Elle raconte. Papa dit : merci. On dit à papa ou maman ce qui s'est passé. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt; aide. Daphné est entourée.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La buée fait un nuage sur la vitre. Une goutte glisse tout doux. Elle laisse un trait brillant. La maison sent la soupe chaude. Une cuillère en bois repose dans la casserole. Le bois est un peu tiède. Dehors, un oiseau se tait. Le village est calme, derrière la vitre. Papa pose un dessin au salon. Le papier fait un petit bruit. Maman reste près de la casserole. Sarah, tu entends la soupe ? Oui, maman. Ça chuchote. Elle est presque prête. Ça sent bon, ici. En ce moment, Sarah veut verser de l'eau. Le pichet est lourd et froid. Le verre est petit et clair. Sarah tient le pichet des deux mains. Le verre bascule. L'eau va sur la table. Ça fait une petite mare. La mare brille. Une goutte tombe aussi par terre. Sarah sent son ventre serré. Elle va vers maman. Maman, l'eau est sur la table. Merci d'avoir raconté. On essuie ensemble. Maman tend une éponge jaune. L'éponge est molle. Sarah appuie tout doux. La table redevient sèche. J'arrive. Papa entre dans la cuisine. Papa, j'ai raconté. L'eau était sur la table. Merci, Sarah. On dit à papa ou maman ce qui s'est passé. Tu as dit juste ce qu'il fallait. Plus tard, le dessin de papa attend au salon. Le papier est fin et crème. Un crayon bleu repose à côté. Sarah veut le regarder de près. Le dessin se froisse un peu. Sarah sent encore son ventre. Elle va vers papa et maman. Le dessin s'est froissé. C'est moi. Merci de raconter. On le lisse ensemble. Papa lisse le papier avec la paume. Maman pose une main sur l'épaule de Sarah. Raconter aide. On dit à papa ou maman. Sarah souffle. Le ventre se desserre. La buée a presque disparu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'eau est sur la table. Que fait Daphné ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'eau est sur la table. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a raconté. Papa a écouté. Maman a écouté. Tu as dit ce qui s'est passé ? Oui, maman. Bravo, Sarah. Tu as fait du bon travail. L'éponge repose près de l'évier. Elle est encore un peu humide. Le dessin est lisse, sur la table. On raconte à papa ou maman. Sarah pose sa main sur le papier. Le papier est doux. Le crayon est à sa place ? Oui, papa. Le crayon bleu ne roule plus.</t>
+          <t>Sarah a raconté. Papa a écouté. Maman a écouté. Tu as dit ce qui s'est passé ? Oui, maman. Bravo, Sarah. L'éponge repose près de l'évier. Elle est encore un peu humide. Le dessin est lisse, sur la table. On raconte à papa ou maman. Sarah pose sa main sur le papier. Le papier est doux. Le crayon est à sa place ? Oui, papa. Le crayon bleu ne roule plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Daphné a raconté. Papa et maman ont écouté. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt; aide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a raconté. Papa a écouté. Maman a écouté. Tu as dit ce qui s'est passé ? Oui, maman. Bravo, Sarah. L'éponge repose près de l'évier. Elle est encore un peu humide. Le dessin est lisse, sur la table. On raconte à papa ou maman. Sarah pose sa main sur le papier. Le papier est doux. Le crayon est à sa place ? Oui, papa. Le crayon bleu ne roule plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,7 +1743,6 @@
 maman|Tu as dit ce qui s'est passé ?
 enfant-f|Oui, maman.
 papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
 narrateur|L'éponge repose près de l'évier.
 narrateur|Elle est encore un peu humide.
 narrateur|Le dessin est lisse, sur la table.
@@ -1784,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Daphné pose l'éponge. Maman lui verse un verre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose l'éponge. Je te verse un verre ? Oui, maman. Maman verse tout doux. Le verre reste droit. Tu as fini d'essuyer ? Oui, papa. Bravo. La soupe chuchote encore. La buée fait un petit nuage. On goûte dans un moment. Ça sent bon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1953,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient son verre des deux mains. La soupe sent bon. Merci d'avoir raconté. On dit à papa ou maman. Oui. L'histoire est finie.</t>
+          <t>Sarah tient son verre des deux mains. La soupe sent bon. Merci d'avoir raconté. On dit à papa ou maman. Oui.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah tient son verre des deux mains. La soupe sent bon. Merci d'avoir raconté. On dit à papa ou maman. Oui.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,8 +2096,7 @@
 narrateur|La soupe sent bon.
 maman|Merci d'avoir raconté.
 papa|On dit à papa ou maman.
-enfant-f|Oui.
-narrateur|L'histoire est finie.</t>
+enfant-f|Oui.</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine puis salon</t>
+          <t>cuisine puis salon, buée sur la vitre, odeur de soupe</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daphné, papa, maman</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>
